--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,87; 40,24</t>
+          <t>33,95; 40,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 33,58</t>
+          <t>26,93; 33,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,77; 40,68</t>
+          <t>32,9; 40,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,65; 54,16</t>
+          <t>48,43; 54,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,33; 51,97</t>
+          <t>45,55; 52,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,85; 61,35</t>
+          <t>55,71; 61,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,0; 47,22</t>
+          <t>43,16; 47,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,37; 43,18</t>
+          <t>38,35; 43,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,37; 52,29</t>
+          <t>47,15; 51,89</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 11,27</t>
+          <t>8,27; 11,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 12,47</t>
+          <t>9,74; 12,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 16,45</t>
+          <t>9,56; 16,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 19,02</t>
+          <t>15,27; 19,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,88; 20,6</t>
+          <t>16,87; 20,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,57; 25,94</t>
+          <t>17,14; 25,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,16; 14,43</t>
+          <t>12,07; 14,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 15,94</t>
+          <t>13,61; 15,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,45; 20,59</t>
+          <t>14,69; 20,58</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,51</t>
+          <t>4,15; 9,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 11,72</t>
+          <t>6,76; 12,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 15,29</t>
+          <t>10,25; 15,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,02; 14,6</t>
+          <t>8,07; 14,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 13,29</t>
+          <t>8,01; 13,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,58; 25,09</t>
+          <t>19,62; 25,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,7</t>
+          <t>6,82; 10,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,56</t>
+          <t>7,95; 11,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,73; 19,4</t>
+          <t>15,64; 19,28</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,66; 18,42</t>
+          <t>15,85; 18,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 16,16</t>
+          <t>13,8; 16,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 19,19</t>
+          <t>13,19; 18,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,71; 30,74</t>
+          <t>27,68; 30,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,47</t>
+          <t>24,24; 27,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,29; 32,53</t>
+          <t>24,49; 32,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,17; 24,26</t>
+          <t>22,15; 24,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 21,55</t>
+          <t>19,38; 21,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,77; 25,57</t>
+          <t>20,4; 25,61</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con dos o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>330070; 392177</t>
+          <t>330859; 393521</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203357; 253316</t>
+          <t>203125; 254452</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168756; 209468</t>
+          <t>169410; 209626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>650822; 724565</t>
+          <t>647962; 723848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>450852; 516961</t>
+          <t>453026; 519795</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>421938; 463527</t>
+          <t>420877; 462181</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>994354; 1092043</t>
+          <t>998082; 1097319</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>671092; 755277</t>
+          <t>670709; 753590</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>601859; 664351</t>
+          <t>599037; 659220</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164646; 221259</t>
+          <t>162378; 221519</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>201364; 258857</t>
+          <t>202205; 258133</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225283; 376658</t>
+          <t>219017; 376109</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>268600; 334263</t>
+          <t>268372; 338673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>335687; 409628</t>
+          <t>335484; 403811</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>370787; 580495</t>
+          <t>383581; 580545</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>452541; 536970</t>
+          <t>449273; 538521</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>550364; 647759</t>
+          <t>553112; 646069</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>654392; 932210</t>
+          <t>665315; 932004</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21144; 45759</t>
+          <t>19974; 44491</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34596; 64097</t>
+          <t>36996; 67604</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65044; 98890</t>
+          <t>66295; 98144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36786; 66976</t>
+          <t>37024; 64604</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43941; 73006</t>
+          <t>43959; 75388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>129310; 165732</t>
+          <t>129592; 166089</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62211; 100533</t>
+          <t>64118; 100142</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86729; 126725</t>
+          <t>87148; 126539</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>205572; 253535</t>
+          <t>204456; 251963</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>535487; 630046</t>
+          <t>542033; 629397</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>462995; 545959</t>
+          <t>466016; 547010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>458049; 662386</t>
+          <t>455442; 654938</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>985003; 1092650</t>
+          <t>983763; 1098936</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>857823; 970431</t>
+          <t>856190; 965757</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>887446; 1188446</t>
+          <t>894853; 1191646</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1546474; 1691601</t>
+          <t>1545084; 1687739</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1343710; 1488955</t>
+          <t>1339408; 1483391</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1476018; 1817035</t>
+          <t>1449643; 1820040</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_2-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,38</t>
+          <t>34,03; 40,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,93; 33,73</t>
+          <t>26,89; 33,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,9; 40,71</t>
+          <t>31,27; 38,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,43; 54,11</t>
+          <t>48,62; 54,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,55; 52,26</t>
+          <t>45,48; 52,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,71; 61,17</t>
+          <t>55,12; 60,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,16; 47,45</t>
+          <t>43,12; 47,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,35; 43,09</t>
+          <t>38,46; 43,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>47,15; 51,89</t>
+          <t>45,93; 50,69</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,27; 11,28</t>
+          <t>8,34; 11,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 12,43</t>
+          <t>9,63; 12,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,56; 16,42</t>
+          <t>14,11; 17,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,27; 19,27</t>
+          <t>15,43; 19,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,87; 20,31</t>
+          <t>16,75; 20,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,14; 25,94</t>
+          <t>24,43; 27,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,07; 14,47</t>
+          <t>12,06; 14,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 15,89</t>
+          <t>13,45; 15,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 20,58</t>
+          <t>19,59; 22,06</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,25</t>
+          <t>4,04; 9,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 12,36</t>
+          <t>6,61; 11,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,18</t>
+          <t>10,26; 15,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 14,09</t>
+          <t>8,11; 14,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 13,73</t>
+          <t>7,98; 13,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,62; 25,15</t>
+          <t>19,99; 25,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 10,66</t>
+          <t>6,72; 10,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,55</t>
+          <t>7,99; 11,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,64; 19,28</t>
+          <t>16,0; 19,98</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 18,4</t>
+          <t>15,66; 18,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,8; 16,2</t>
+          <t>13,77; 16,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,19; 18,97</t>
+          <t>16,83; 19,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27,68; 30,92</t>
+          <t>27,69; 30,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,24; 27,34</t>
+          <t>24,33; 27,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,49; 32,61</t>
+          <t>31,04; 33,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,15; 24,2</t>
+          <t>22,23; 24,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,38; 21,47</t>
+          <t>19,6; 21,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,4; 25,61</t>
+          <t>24,5; 26,4</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189009</t>
+          <t>201389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>442456</t>
+          <t>474485</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>631465</t>
+          <t>675875</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>330859; 393521</t>
+          <t>331637; 393956</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>203125; 254452</t>
+          <t>202865; 250826</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>169410; 209626</t>
+          <t>180928; 224048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>647962; 723848</t>
+          <t>650422; 722662</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>453026; 519795</t>
+          <t>452410; 518093</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>420877; 462181</t>
+          <t>453120; 496925</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>998082; 1097319</t>
+          <t>997074; 1095226</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>670709; 753590</t>
+          <t>672582; 755756</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>599037; 659220</t>
+          <t>643339; 709971</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324037</t>
+          <t>348842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>507111</t>
+          <t>565007</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>831148</t>
+          <t>913850</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>162378; 221519</t>
+          <t>163728; 218038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>202205; 258133</t>
+          <t>199922; 259866</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>219017; 376109</t>
+          <t>314669; 386286</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>268372; 338673</t>
+          <t>271295; 339910</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>335484; 403811</t>
+          <t>333090; 406805</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>383581; 580545</t>
+          <t>530461; 604506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>449273; 538521</t>
+          <t>449025; 535647</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>553112; 646069</t>
+          <t>546898; 647583</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>665315; 932004</t>
+          <t>862341; 971056</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81429</t>
+          <t>90092</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>147890</t>
+          <t>167281</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>229320</t>
+          <t>257374</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19974; 44491</t>
+          <t>19454; 43407</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36996; 67604</t>
+          <t>36160; 64507</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66295; 98144</t>
+          <t>73039; 108638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37024; 64604</t>
+          <t>37179; 66184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>43959; 75388</t>
+          <t>43795; 72483</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>129592; 166089</t>
+          <t>146891; 187223</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64118; 100142</t>
+          <t>63145; 99870</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87148; 126539</t>
+          <t>87615; 129609</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>204456; 251963</t>
+          <t>231490; 289032</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>594475</t>
+          <t>640324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1097458</t>
+          <t>1206774</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1691933</t>
+          <t>1847098</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>542033; 629397</t>
+          <t>535649; 632557</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>466016; 547010</t>
+          <t>465036; 548545</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>455442; 654938</t>
+          <t>592505; 688425</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>983763; 1098936</t>
+          <t>984299; 1094586</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>856190; 965757</t>
+          <t>859304; 969839</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>894853; 1191646</t>
+          <t>1157126; 1255524</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1545084; 1687739</t>
+          <t>1550211; 1689900</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1339408; 1483391</t>
+          <t>1354113; 1489906</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1449643; 1820040</t>
+          <t>1775895; 1913625</t>
         </is>
       </c>
     </row>
